--- a/tables/Table2_Hub_Genes_AUC.xlsx
+++ b/tables/Table2_Hub_Genes_AUC.xlsx
@@ -1,152 +1,103 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\ZWHQD_HFrEF\tables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0E8DF4-9DE9-4E5D-8105-9A22EF0BCDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t>Gene</t>
-  </si>
-  <si>
-    <t>MCC</t>
-  </si>
-  <si>
-    <t>MNC</t>
-  </si>
-  <si>
-    <t>Degree</t>
-  </si>
-  <si>
-    <t>Train_AUC</t>
-  </si>
-  <si>
-    <t>Test_AUC</t>
-  </si>
-  <si>
-    <t>STAT3</t>
-  </si>
-  <si>
-    <t>HIF1A</t>
-  </si>
-  <si>
-    <t>KDR</t>
-  </si>
-  <si>
-    <t>MMP2</t>
-  </si>
-  <si>
-    <t>SERPINE1</t>
-  </si>
-  <si>
-    <t>BCL2L1</t>
-  </si>
-  <si>
-    <t>ACE</t>
-  </si>
-  <si>
-    <t>AGTR1</t>
-  </si>
-  <si>
-    <t>SLC2A1</t>
-  </si>
-  <si>
-    <t>KIT</t>
-  </si>
-  <si>
-    <t>CDKN1A</t>
-  </si>
-  <si>
-    <t>JAK1</t>
-  </si>
-  <si>
-    <t>ABCG2</t>
-  </si>
-  <si>
-    <t>CCND2</t>
-  </si>
-  <si>
-    <t>CASP1</t>
-  </si>
-  <si>
-    <t>FGF1</t>
-  </si>
-  <si>
-    <t>ANPEP</t>
-  </si>
-  <si>
-    <t>EDNRB</t>
-  </si>
-  <si>
-    <t>GSE116250_AUC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GSE19303_AUC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AUC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GSE141910_Train</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GSE141910_Test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GSE116250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GSE19303</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t xml:space="preserve">Gene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MNC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_AUC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test_AUC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIF1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERPINE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCL2L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGTR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC2A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDKN1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCG2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCND2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FGF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANPEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDNRB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -169,26 +120,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -470,16 +408,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,417 +431,369 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1748</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>20</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>20</v>
       </c>
-      <c r="E2">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="F2">
-        <v>0.83599999999999997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E2" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.836</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>1740</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>17</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>17</v>
       </c>
-      <c r="E3">
-        <v>0.85399999999999998</v>
-      </c>
-      <c r="F3">
-        <v>0.84199999999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E3" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.842</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>1404</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>15</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>15</v>
       </c>
-      <c r="E4">
-        <v>0.81699999999999995</v>
-      </c>
-      <c r="F4">
+      <c r="E4" t="n">
+        <v>0.817</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.85</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>1249</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>11</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>12</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>0.79</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>0.749</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>877</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>10</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>11</v>
       </c>
-      <c r="E6">
-        <v>0.73099999999999998</v>
-      </c>
-      <c r="F6">
+      <c r="E6" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.76</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>793</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>12</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>13</v>
       </c>
-      <c r="E7">
-        <v>0.92700000000000005</v>
-      </c>
-      <c r="F7">
-        <v>0.92200000000000004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="E7" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.922</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>767</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>11</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>14</v>
       </c>
-      <c r="E8">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="F8">
-        <v>0.92400000000000004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E8" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.924</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>763</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>10</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>11</v>
       </c>
-      <c r="E9">
-        <v>0.83899999999999997</v>
-      </c>
-      <c r="F9">
-        <v>0.84599999999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E9" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.846</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>393</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>12</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>13</v>
       </c>
-      <c r="E10">
-        <v>0.86799999999999999</v>
-      </c>
-      <c r="F10">
+      <c r="E10" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.87</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>302</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>13</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>13</v>
       </c>
-      <c r="E11">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="F11">
-        <v>0.83499999999999996</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E11" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.835</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>288</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>9</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>9</v>
       </c>
-      <c r="E12">
-        <v>0.76900000000000002</v>
-      </c>
-      <c r="F12">
-        <v>0.77100000000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="E12" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.771</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>264</v>
       </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-      <c r="D13">
-        <v>7</v>
-      </c>
-      <c r="E13">
-        <v>0.95399999999999996</v>
-      </c>
-      <c r="F13">
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.95</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    <row r="14">
+      <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>242</v>
       </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-      <c r="D14">
-        <v>7</v>
-      </c>
-      <c r="E14">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="F14">
-        <v>0.94599999999999995</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.946</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>144</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>6</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>6</v>
       </c>
-      <c r="E15">
-        <v>0.84099999999999997</v>
-      </c>
-      <c r="F15">
+      <c r="E15" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.89</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>20</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>78</v>
       </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
-      <c r="D16">
-        <v>7</v>
-      </c>
-      <c r="E16">
-        <v>0.84699999999999998</v>
-      </c>
-      <c r="F16">
-        <v>0.89300000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.893</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
         <v>21</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>72</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>6</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>6</v>
       </c>
-      <c r="E17">
-        <v>0.92100000000000004</v>
-      </c>
-      <c r="F17">
+      <c r="E17" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.93</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>22</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>38</v>
       </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-      <c r="D18">
-        <v>7</v>
-      </c>
-      <c r="E18">
-        <v>0.86799999999999999</v>
-      </c>
-      <c r="F18">
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.84</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="19">
+      <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>11</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>5</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>6</v>
       </c>
-      <c r="E19">
-        <v>0.95499999999999996</v>
-      </c>
-      <c r="F19">
-        <v>0.93799999999999994</v>
+      <c r="E19" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.938</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A9FCA13-A94B-45AB-82E9-61AD9A1A5E9D}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C1" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>